--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B621C18F-A7E7-4A40-9007-E380F413E518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5056013E-3655-42BB-84D8-693FB125E962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="125">
   <si>
     <t>answer_value</t>
   </si>
@@ -1453,7 +1453,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>aaa</t>
+    <t>固定資産税や印紙税などの税金</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シサンゼイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>インシゼイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゼイキン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2231,6 +2243,9 @@
       <c r="C19" s="1" t="s">
         <v>124</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5056013E-3655-42BB-84D8-693FB125E962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E00585-CA7E-48B8-8F04-640A24158D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="分類問題" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="171">
   <si>
     <t>answer_value</t>
   </si>
@@ -168,13 +168,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>応接セット、机、椅子、パソコン、ＦＡＸ、プリンター、コピ－機等</t>
-    <rPh sb="30" eb="31">
-      <t>トウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>借入金</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1465,6 +1458,682 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>ゼイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>応接セット、机、椅子、パソコン、プリンター、コピ－機等</t>
+    <rPh sb="26" eb="27">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受取手数料</t>
+    <rPh sb="2" eb="5">
+      <t>テスウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>本業外で、仲介、斡旋、代行などにより受取った手数料</t>
+    <rPh sb="18" eb="20">
+      <t>ウケト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>販売目的で商品を購入した際に使用する勘定科目</t>
+    <rPh sb="0" eb="2">
+      <t>ハンバイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上原価</t>
+    <rPh sb="0" eb="4">
+      <t>ウリアゲゲンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売れた（顧客に引渡した）商品の原価</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒキワタ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支払手数料</t>
+    <rPh sb="0" eb="2">
+      <t>シハライ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>テスウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銀行振込、クレジットカード決済などのサービス利用時に外部に支払う際に使用する勘定科目</t>
+    <rPh sb="26" eb="28">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑費</t>
+    <rPh sb="0" eb="2">
+      <t>ザッピ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他のどの勘定科目にも当てはまらない、少額かつ一時的な出費</t>
+  </si>
+  <si>
+    <t>売掛金</t>
+    <rPh sb="0" eb="3">
+      <t>ウリカケキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上代金の未回収分で、後日受け取る予定のもの</t>
+    <rPh sb="0" eb="4">
+      <t>ウリアゲダイキン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ミカイシュウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゴジツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕入代金の未払い分で、後日支払う予定のもの</t>
+    <rPh sb="0" eb="2">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ダイキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ミバラ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゴジツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>繰越商品</t>
+    <rPh sb="0" eb="4">
+      <t>クリコシショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期末時点で販売されずに在庫として残っいる商品の原価</t>
+    <rPh sb="0" eb="4">
+      <t>キマツジテン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンバイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゲンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ仕入は費用なのか？</t>
+    <rPh sb="2" eb="4">
+      <t>シイレ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストにそう書いてあるから</t>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上を得るために出て行ったことにするから</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ繰越商品は資産なのか？</t>
+    <rPh sb="2" eb="6">
+      <t>クリコシショウヒン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品だから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品を仕入れたから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３分法を採用しているから</t>
+    <rPh sb="1" eb="2">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３分法の場合、一旦すべて売れたことにして、期末に在庫を繰越商品として資産として処理します。</t>
+    <rPh sb="1" eb="3">
+      <t>ブンホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イッタン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キマツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>クリコシショウヒン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上原価対立法を採用しているから</t>
+    <rPh sb="0" eb="4">
+      <t>ウリアゲゲンカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイリツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お店の商品だから</t>
+    <rPh sb="1" eb="2">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期末時点で所有している在庫を表します。会社に残っているモノなので資産に該当します。</t>
+    <rPh sb="0" eb="2">
+      <t>キマツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジテン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショユウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイシャ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ガイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだその会社の商品だから</t>
+    <rPh sb="4" eb="6">
+      <t>カイシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売れた商品の原価だから</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだ売上げていないから</t>
+    <rPh sb="2" eb="4">
+      <t>ウリア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ消耗品を買うと費用なのか？</t>
+    <rPh sb="2" eb="5">
+      <t>ショウモウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだ使っていないから</t>
+    <rPh sb="2" eb="3">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額が少額で、資産計上する必要がないから</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウガク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>シサンケイジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これから使う文房具類だから</t>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ブンボウグ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使い切ったから</t>
+    <rPh sb="0" eb="1">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>消耗品も厳密には購入時は、会社の所有物ですが、使い切ることが明白で少額なので、消耗品費として費用処理します。</t>
+    <rPh sb="0" eb="3">
+      <t>ショウモウヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゲンミツ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>コウニュウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイシャ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ショユウブツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>メイハク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ショウガク</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>ショウモウヒンヒ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ売掛金は資産なのか？</t>
+    <rPh sb="2" eb="5">
+      <t>ウリカケキン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上代金で回収した分だから</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ダイキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来、お客さんに請求できるから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来、お客さんに請求されるから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売掛金とは売上代金でまだお客さんからお金を頂いていない分で、将来請求し、お金に変わります。</t>
+    <rPh sb="0" eb="3">
+      <t>ウリカケキン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ウリアゲダイキン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イタダ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セイキュウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ買掛金は負債なのか？</t>
+    <rPh sb="2" eb="5">
+      <t>カイカケキン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上代金だから</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ダイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来、支払う義務があるから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ギム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来、受取る権利があるから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ウケト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来の仕入だから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シイレ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来の売上だから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ウリアゲ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>買掛金とは仕入代金でまだ仕入先に支払っていない分で、将来請求され、お金を支払います。</t>
+    <rPh sb="0" eb="3">
+      <t>カイカケキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ダイキン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シイレ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セイキュウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シハライ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1473,7 +2142,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1535,6 +2204,21 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1558,7 +2242,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1588,6 +2272,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1923,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0246E57E-1A7C-477B-962D-8E28C390228D}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.875" style="1" bestFit="1" customWidth="1"/>
@@ -1944,10 +2634,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -1958,10 +2648,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -1978,7 +2668,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -1995,7 +2685,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -2012,7 +2702,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -2029,7 +2719,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2040,13 +2730,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2060,10 +2750,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2074,13 +2764,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2091,13 +2781,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2108,13 +2798,13 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2125,13 +2815,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -2142,13 +2832,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2159,13 +2849,13 @@
         <v>5</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -2176,13 +2866,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -2193,13 +2883,13 @@
         <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -2210,10 +2900,11 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>121</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C17" s="10"/>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -2224,10 +2915,11 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C18" s="10"/>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -2238,17 +2930,555 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
+    </row>
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="1">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="1">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="1">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="1">
+        <v>1</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="1">
+        <v>2</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="1">
+        <v>1</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C28" s="10"/>
+    </row>
+    <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C29" s="10"/>
+    </row>
+    <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C31" s="10"/>
+    </row>
+    <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C32" s="10"/>
+    </row>
+    <row r="33" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C33" s="10"/>
+    </row>
+    <row r="34" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C34" s="10"/>
+    </row>
+    <row r="35" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C35" s="10"/>
+    </row>
+    <row r="36" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="10"/>
+    </row>
+    <row r="37" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C37" s="10"/>
+    </row>
+    <row r="38" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C38" s="10"/>
+    </row>
+    <row r="39" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C39" s="10"/>
+    </row>
+    <row r="40" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C40" s="10"/>
+    </row>
+    <row r="41" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C41" s="10"/>
+    </row>
+    <row r="42" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C42" s="10"/>
+    </row>
+    <row r="43" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C43" s="10"/>
+    </row>
+    <row r="44" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C44" s="10"/>
+    </row>
+    <row r="45" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C45" s="10"/>
+    </row>
+    <row r="46" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C46" s="10"/>
+    </row>
+    <row r="47" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C47" s="10"/>
+    </row>
+    <row r="48" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C48" s="10"/>
+    </row>
+    <row r="49" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C49" s="10"/>
+    </row>
+    <row r="50" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C50" s="10"/>
+    </row>
+    <row r="51" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C51" s="10"/>
+    </row>
+    <row r="52" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C52" s="10"/>
+    </row>
+    <row r="53" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C53" s="10"/>
+    </row>
+    <row r="54" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C54" s="10"/>
+    </row>
+    <row r="55" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C55" s="10"/>
+    </row>
+    <row r="56" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C56" s="10"/>
+    </row>
+    <row r="57" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C57" s="10"/>
+    </row>
+    <row r="58" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C58" s="10"/>
+    </row>
+    <row r="59" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C59" s="10"/>
+    </row>
+    <row r="60" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C60" s="10"/>
+    </row>
+    <row r="61" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C61" s="10"/>
+    </row>
+    <row r="62" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C62" s="10"/>
+    </row>
+    <row r="63" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C63" s="10"/>
+    </row>
+    <row r="64" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C64" s="10"/>
+    </row>
+    <row r="65" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C65" s="10"/>
+    </row>
+    <row r="66" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C66" s="10"/>
+    </row>
+    <row r="67" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C67" s="10"/>
+    </row>
+    <row r="68" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C68" s="10"/>
+    </row>
+    <row r="69" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C69" s="10"/>
+    </row>
+    <row r="70" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C70" s="10"/>
+    </row>
+    <row r="71" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C71" s="10"/>
+    </row>
+    <row r="72" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C72" s="10"/>
+    </row>
+    <row r="73" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C73" s="10"/>
+    </row>
+    <row r="74" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C74" s="10"/>
+    </row>
+    <row r="75" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C75" s="10"/>
+    </row>
+    <row r="76" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C76" s="10"/>
+    </row>
+    <row r="77" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C77" s="10"/>
+    </row>
+    <row r="78" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C78" s="10"/>
+    </row>
+    <row r="79" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C79" s="10"/>
+    </row>
+    <row r="80" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C80" s="10"/>
+    </row>
+    <row r="81" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C81" s="10"/>
+    </row>
+    <row r="82" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C82" s="10"/>
+    </row>
+    <row r="83" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C83" s="10"/>
+    </row>
+    <row r="84" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C84" s="10"/>
+    </row>
+    <row r="85" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C85" s="10"/>
+    </row>
+    <row r="86" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C86" s="10"/>
+    </row>
+    <row r="87" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C87" s="10"/>
+    </row>
+    <row r="88" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C88" s="10"/>
+    </row>
+    <row r="89" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C89" s="10"/>
+    </row>
+    <row r="90" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C90" s="10"/>
+    </row>
+    <row r="91" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C91" s="10"/>
+    </row>
+    <row r="92" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C92" s="10"/>
+    </row>
+    <row r="93" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C93" s="10"/>
+    </row>
+    <row r="94" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C94" s="10"/>
+    </row>
+    <row r="95" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C95" s="10"/>
+    </row>
+    <row r="96" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C96" s="10"/>
+    </row>
+    <row r="97" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C97" s="10"/>
+    </row>
+    <row r="98" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C98" s="10"/>
+    </row>
+    <row r="99" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C99" s="10"/>
+    </row>
+    <row r="100" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C100" s="10"/>
+    </row>
+    <row r="101" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C101" s="10"/>
+    </row>
+    <row r="102" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C102" s="10"/>
+    </row>
+    <row r="103" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C103" s="10"/>
+    </row>
+    <row r="104" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C104" s="10"/>
+    </row>
+    <row r="105" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C105" s="10"/>
+    </row>
+    <row r="106" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C106" s="10"/>
+    </row>
+    <row r="107" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C107" s="10"/>
+    </row>
+    <row r="108" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C108" s="10"/>
+    </row>
+    <row r="109" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C109" s="10"/>
+    </row>
+    <row r="110" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C110" s="10"/>
+    </row>
+    <row r="111" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C111" s="10"/>
+    </row>
+    <row r="112" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C112" s="10"/>
+    </row>
+    <row r="113" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C113" s="10"/>
+    </row>
+    <row r="114" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C114" s="10"/>
+    </row>
+    <row r="115" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C115" s="10"/>
+    </row>
+    <row r="116" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C116" s="10"/>
+    </row>
+    <row r="117" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C117" s="10"/>
+    </row>
+    <row r="118" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C118" s="10"/>
+    </row>
+    <row r="119" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C119" s="10"/>
+    </row>
+    <row r="120" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C120" s="10"/>
+    </row>
+    <row r="121" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C121" s="10"/>
+    </row>
+    <row r="122" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C122" s="10"/>
+    </row>
+    <row r="123" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C123" s="10"/>
+    </row>
+    <row r="124" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C124" s="10"/>
+    </row>
+    <row r="125" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C125" s="10"/>
+    </row>
+    <row r="126" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C126" s="10"/>
+    </row>
+    <row r="127" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C127" s="10"/>
+    </row>
+    <row r="128" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C128" s="10"/>
+    </row>
+    <row r="129" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C129" s="10"/>
+    </row>
+    <row r="130" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C130" s="10"/>
+    </row>
+    <row r="131" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C131" s="10"/>
+    </row>
+    <row r="132" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C132" s="10"/>
+    </row>
+    <row r="133" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C133" s="10"/>
+    </row>
+    <row r="134" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C134" s="10"/>
+    </row>
+    <row r="135" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C135" s="10"/>
+    </row>
+    <row r="136" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C136" s="10"/>
+    </row>
+    <row r="137" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C137" s="10"/>
+    </row>
+    <row r="138" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C138" s="10"/>
+    </row>
+    <row r="139" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C139" s="10"/>
+    </row>
+    <row r="140" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C140" s="10"/>
+    </row>
+    <row r="141" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C141" s="10"/>
+    </row>
+    <row r="142" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C142" s="10"/>
+    </row>
+    <row r="143" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C143" s="10"/>
+    </row>
+    <row r="144" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C144" s="10"/>
+    </row>
+    <row r="145" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C145" s="10"/>
+    </row>
+    <row r="146" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C146" s="10"/>
+    </row>
+    <row r="147" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C147" s="10"/>
+    </row>
+    <row r="148" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C148" s="10"/>
+    </row>
+    <row r="149" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C149" s="10"/>
+    </row>
+    <row r="150" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C150" s="10"/>
+    </row>
+    <row r="151" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C151" s="10"/>
+    </row>
+    <row r="152" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C152" s="10"/>
+    </row>
+    <row r="153" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C153" s="10"/>
+    </row>
+    <row r="154" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C154" s="10"/>
+    </row>
+    <row r="155" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C155" s="10"/>
+    </row>
+    <row r="156" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C156" s="10"/>
+    </row>
+    <row r="157" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C157" s="10"/>
+    </row>
+    <row r="158" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C158" s="10"/>
+    </row>
+    <row r="159" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C159" s="10"/>
+    </row>
+    <row r="160" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C160" s="10"/>
+    </row>
+    <row r="161" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C161" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2258,61 +3488,64 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52B2431-11E2-4394-A320-3C115695266D}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="27.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="117" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
         <v>58</v>
-      </c>
-      <c r="B1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" t="s">
-        <v>59</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>44</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -2320,25 +3553,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>52</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -2346,25 +3579,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>51</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" t="s">
-        <v>52</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -2372,25 +3605,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
         <v>113</v>
       </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>114</v>
-      </c>
-      <c r="E5" t="s">
-        <v>115</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -2398,28 +3631,184 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
         <v>117</v>
       </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>118</v>
-      </c>
       <c r="D6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" t="s">
         <v>114</v>
-      </c>
-      <c r="E6" t="s">
-        <v>115</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H6">
         <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2438,54 +3827,54 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
-        <v>60</v>
-      </c>
       <c r="I1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
         <v>61</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>62</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>64</v>
-      </c>
-      <c r="E2" t="s">
-        <v>65</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2493,25 +3882,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
         <v>67</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>68</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2519,25 +3908,25 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
       <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
         <v>86</v>
-      </c>
-      <c r="D4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" t="s">
-        <v>87</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -2545,25 +3934,25 @@
     </row>
     <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" t="s">
         <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>75</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2571,25 +3960,25 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
         <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>80</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -2608,104 +3997,104 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" t="s">
         <v>90</v>
       </c>
-      <c r="C1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>95</v>
       </c>
-      <c r="K1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>96</v>
       </c>
-      <c r="M1" t="s">
-        <v>97</v>
-      </c>
       <c r="N1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
         <v>98</v>
-      </c>
-      <c r="B2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" t="s">
-        <v>99</v>
       </c>
       <c r="D2">
         <v>100000</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G2">
         <v>30000</v>
       </c>
       <c r="K2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M2">
         <v>70000</v>
       </c>
       <c r="N2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" t="s">
         <v>109</v>
-      </c>
-      <c r="B3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" t="s">
-        <v>110</v>
       </c>
       <c r="D3">
         <v>100000</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3">
         <v>100000</v>
@@ -2713,22 +4102,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4">
         <v>200000</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G4">
         <v>200000</v>

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E00585-CA7E-48B8-8F04-640A24158D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BE762B-9F1F-4BA3-8660-30CB1A39A5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="分類問題" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="208">
   <si>
     <t>answer_value</t>
   </si>
@@ -1202,28 +1202,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>仕入という費用の発生と現金という資産の減少です。</t>
-    <rPh sb="0" eb="2">
-      <t>シイレ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒヨウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>シサン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ゲンショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現金,買掛金,仕入,売上</t>
     <rPh sb="0" eb="2">
       <t>ゲンキン</t>
@@ -2134,6 +2112,614 @@
     </rPh>
     <rPh sb="36" eb="38">
       <t>シハライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ商品を仕入れたら費用になるのか？</t>
+    <rPh sb="2" eb="4">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いずれ売れるので売れたことにするから</t>
+    <rPh sb="3" eb="4">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品という資産が減少するから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>店頭に商品が並ぶから</t>
+    <rPh sb="0" eb="2">
+      <t>テントウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>既存の商品が減少したから</t>
+    <rPh sb="0" eb="2">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ消耗品は資産ではないのか？</t>
+    <rPh sb="2" eb="5">
+      <t>ショウモウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>消耗品は費用だから</t>
+    <rPh sb="0" eb="3">
+      <t>ショウモウヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>消耗品は消耗するから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウモウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウモウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>消耗したことにするから</t>
+    <rPh sb="0" eb="2">
+      <t>ショウモウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>消耗品を消耗してないから</t>
+    <rPh sb="0" eb="3">
+      <t>ショウモウヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウモウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備品という資産の増加と現金という資産の減少です。</t>
+    <rPh sb="0" eb="2">
+      <t>ビヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜ売上げた時、商品の減少を仕訳しないのか？</t>
+    <rPh sb="2" eb="4">
+      <t>ウリア</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シワケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上の話だから</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハナシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕入時に仕訳済みだから</t>
+    <rPh sb="0" eb="3">
+      <t>シイレジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シワケ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>スミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３分法の場合、仕入時に売上原価として仕訳済みです。決算時に売れ残りを繰越商品として資産として処理します。</t>
+    <rPh sb="1" eb="3">
+      <t>ブンホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シイレジ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ウリアゲゲンカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シワケ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ケッサンジ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>クリコシ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３分法を採用しているから</t>
+    <rPh sb="1" eb="3">
+      <t>ブンホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上と商品の減少は関係ないから</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上げた時に商品は減らないから</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヘ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いずれ商品は売れるから</t>
+    <rPh sb="3" eb="5">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世の中それが常だから</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金という資産の増加と売上という収益の発生です。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウエキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金50,000を借入れた。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カリイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,貸付金,借入金,備品</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カシツケキン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>カリイレキン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ビヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>借入金</t>
+    <rPh sb="0" eb="3">
+      <t>カリイレキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金という資産の増加と借入金という負債の増加です。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カリイレキン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>フサイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>給料30,000を現金で支払った。</t>
+    <rPh sb="0" eb="2">
+      <t>キュウリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,資本金,給料,雑費）</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シホンキン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キュウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ザッピ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>給料</t>
+    <rPh sb="0" eb="2">
+      <t>キュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>給料という費用の発生と現金という資産の減少です。</t>
+    <rPh sb="0" eb="2">
+      <t>キュウリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手数料15,000を現金で受取った。</t>
+    <rPh sb="0" eb="3">
+      <t>テスウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ウケト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,支払手数料,手数料,受取手数料）</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>テスウリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>テスウリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ウケトリ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>テスウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受取手数料</t>
+    <rPh sb="0" eb="2">
+      <t>ウケトリ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>テスウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金という資産の増加と受取手数料という収益の発生です。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="11" eb="16">
+      <t>ウケトリテスウリョウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウエキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕入という費用の発生と現金という資産の減少、買掛金という負債の増加です。</t>
+    <rPh sb="0" eb="2">
+      <t>シイレ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カイカケキン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フサイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>借入金のうち5,000を返済し、利息100とともに現金で支払った。</t>
+    <rPh sb="0" eb="2">
+      <t>カリイレ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンサイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>リソク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,借入金,支払利息,受取利息）</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カリイレキン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シハライ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リソク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ウケトリ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>リソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支払利息</t>
+    <rPh sb="0" eb="2">
+      <t>シハライ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>借入金という負債の増加と支払利息という費用の発生、現金という資産の減少です。</t>
+    <rPh sb="0" eb="3">
+      <t>カリイレキン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フサイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シハライ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>リソク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゲンショウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2637,7 +3223,7 @@
         <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -2648,7 +3234,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -2750,7 +3336,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>32</v>
@@ -2900,7 +3486,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="1" t="s">
@@ -2915,7 +3501,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="1" t="s">
@@ -2930,10 +3516,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>36</v>
@@ -2947,10 +3533,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>35</v>
@@ -2967,7 +3553,7 @@
         <v>98</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>36</v>
@@ -2981,10 +3567,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>36</v>
@@ -2998,10 +3584,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>36</v>
@@ -3015,10 +3601,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>36</v>
@@ -3032,10 +3618,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>32</v>
@@ -3052,7 +3638,7 @@
         <v>100</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>33</v>
@@ -3066,10 +3652,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -3488,7 +4074,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52B2431-11E2-4394-A320-3C115695266D}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="27.625" bestFit="1" customWidth="1"/>
@@ -3522,7 +4108,7 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -3585,7 +4171,7 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
         <v>55</v>
@@ -3605,7 +4191,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3614,16 +4200,16 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" t="s">
         <v>113</v>
-      </c>
-      <c r="E5" t="s">
-        <v>114</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -3631,25 +4217,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" t="s">
         <v>113</v>
-      </c>
-      <c r="E6" t="s">
-        <v>114</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -3657,7 +4243,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
@@ -3666,16 +4252,16 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E7" t="s">
         <v>140</v>
-      </c>
-      <c r="E7" t="s">
-        <v>141</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -3683,25 +4269,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" t="s">
         <v>142</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>150</v>
       </c>
-      <c r="C8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>151</v>
       </c>
-      <c r="E8" t="s">
-        <v>152</v>
-      </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -3709,25 +4295,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" t="s">
         <v>144</v>
       </c>
-      <c r="C9" t="s">
-        <v>145</v>
-      </c>
       <c r="D9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" t="s">
         <v>147</v>
-      </c>
-      <c r="E9" t="s">
-        <v>148</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -3735,25 +4321,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" t="s">
         <v>153</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>154</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>155</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>156</v>
-      </c>
-      <c r="E10" t="s">
-        <v>157</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -3761,25 +4347,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
         <v>159</v>
       </c>
-      <c r="B11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>160</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>161</v>
-      </c>
-      <c r="E11" t="s">
-        <v>162</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -3787,28 +4373,126 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" t="s">
         <v>166</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>167</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>168</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>169</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>170</v>
       </c>
-      <c r="H12">
-        <v>1</v>
+      <c r="B13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>157</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3851,7 +4535,7 @@
         <v>80</v>
       </c>
       <c r="J1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -3992,7 +4676,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C41FE44F-CD0E-49E1-9F40-FF2D55A2ECFA}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -4039,7 +4723,7 @@
         <v>59</v>
       </c>
       <c r="O1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
@@ -4056,7 +4740,7 @@
         <v>100000</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
         <v>103</v>
@@ -4065,7 +4749,7 @@
         <v>30000</v>
       </c>
       <c r="K2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L2" t="s">
         <v>100</v>
@@ -4074,24 +4758,24 @@
         <v>70000</v>
       </c>
       <c r="N2" t="s">
-        <v>104</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
         <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3">
         <v>100000</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
         <v>103</v>
@@ -4099,10 +4783,13 @@
       <c r="G3">
         <v>100000</v>
       </c>
+      <c r="N3" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
         <v>99</v>
@@ -4114,13 +4801,129 @@
         <v>200000</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4">
         <v>200000</v>
+      </c>
+      <c r="N4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5">
+        <v>50000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5">
+        <v>50000</v>
+      </c>
+      <c r="N5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6">
+        <v>30000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6">
+        <v>30000</v>
+      </c>
+      <c r="N6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7">
+        <v>15000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G7">
+        <v>15000</v>
+      </c>
+      <c r="N7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8">
+        <v>5000</v>
+      </c>
+      <c r="E8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <v>5100</v>
+      </c>
+      <c r="H8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I8" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="N8" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BE762B-9F1F-4BA3-8660-30CB1A39A5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45BF3AD-8CF6-4683-A04E-C55BC4C841FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
@@ -657,9 +657,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>手許資金3,000,000円で、株式会社東京商事を設立した。</t>
-  </si>
-  <si>
     <t>借：現金 / 貸 : 借入金</t>
     <rPh sb="0" eb="1">
       <t>カ</t>
@@ -1135,28 +1132,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>商品100,000を仕入れ、30,000は現金で支払い残りは掛けとした。</t>
-    <rPh sb="0" eb="2">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シハラ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ノコ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>仕入</t>
     <rPh sb="0" eb="2">
       <t>シイ</t>
@@ -1244,44 +1219,9 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>備品100,000を購入し、現金で支払った。</t>
+    <t>備品</t>
     <rPh sb="0" eb="2">
       <t>ビヒン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>コウニュウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シハラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>備品</t>
-    <rPh sb="0" eb="2">
-      <t>ビヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>商品200,000を売上げ、現金を受け取った。</t>
-    <rPh sb="0" eb="2">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ウリア</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2425,16 +2365,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>現金50,000を借入れた。</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カリイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現金,貸付金,借入金,備品</t>
     <rPh sb="0" eb="2">
       <t>ゲンキン</t>
@@ -2480,19 +2410,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>給料30,000を現金で支払った。</t>
-    <rPh sb="0" eb="2">
-      <t>キュウリョウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シハラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現金,資本金,給料,雑費）</t>
     <rPh sb="0" eb="2">
       <t>ゲンキン</t>
@@ -2538,19 +2455,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>手数料15,000を現金で受取った。</t>
-    <rPh sb="0" eb="3">
-      <t>テスウリョウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ウケト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現金,支払手数料,手数料,受取手数料）</t>
     <rPh sb="0" eb="2">
       <t>ゲンキン</t>
@@ -2632,28 +2536,6 @@
     </rPh>
     <rPh sb="31" eb="33">
       <t>ゾウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>借入金のうち5,000を返済し、利息100とともに現金で支払った。</t>
-    <rPh sb="0" eb="2">
-      <t>カリイレ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>キン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヘンサイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>リソク</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シハラ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2721,6 +2603,125 @@
     <rPh sb="33" eb="35">
       <t>ゲンショウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品100を仕入れ、30は現金で支払い残りは掛けとした。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備品100を購入し、現金で支払った。</t>
+    <rPh sb="0" eb="2">
+      <t>ビヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品200を売上げ、現金を受け取った。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ウリア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金50を借入れた。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カリイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>給料30を現金で支払った。</t>
+    <rPh sb="0" eb="2">
+      <t>キュウリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手数料15を現金で受取った。</t>
+    <rPh sb="0" eb="3">
+      <t>テスウリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ウケト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>借入金のうち50を返済し、利息1とともに現金で支払った。</t>
+    <rPh sb="0" eb="2">
+      <t>カリイレ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンサイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>リソク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手許資金3,000,000円で、株式会社東京商事を設立した。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3223,7 +3224,7 @@
         <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -3234,7 +3235,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -3336,7 +3337,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>32</v>
@@ -3486,7 +3487,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="1" t="s">
@@ -3501,7 +3502,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="1" t="s">
@@ -3516,10 +3517,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>36</v>
@@ -3533,10 +3534,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>35</v>
@@ -3550,10 +3551,10 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>36</v>
@@ -3567,10 +3568,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>36</v>
@@ -3584,10 +3585,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>36</v>
@@ -3601,10 +3602,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>36</v>
@@ -3618,10 +3619,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>32</v>
@@ -3635,10 +3636,10 @@
         <v>2</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>33</v>
@@ -3652,10 +3653,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -4108,7 +4109,7 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -4171,7 +4172,7 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
         <v>55</v>
@@ -4191,7 +4192,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -4200,16 +4201,16 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -4217,25 +4218,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -4243,7 +4244,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
@@ -4252,16 +4253,16 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -4269,25 +4270,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -4295,25 +4296,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" t="s">
         <v>143</v>
-      </c>
-      <c r="C9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" t="s">
-        <v>147</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -4321,25 +4322,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" t="s">
         <v>152</v>
-      </c>
-      <c r="B10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E10" t="s">
-        <v>156</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -4347,25 +4348,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -4373,25 +4374,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" t="s">
         <v>163</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>165</v>
-      </c>
-      <c r="C12" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E12" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>169</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -4399,25 +4400,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" t="s">
         <v>170</v>
       </c>
-      <c r="B13" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" t="s">
-        <v>174</v>
-      </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -4425,25 +4426,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" t="s">
         <v>175</v>
       </c>
-      <c r="B14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" t="s">
-        <v>176</v>
-      </c>
-      <c r="D14" t="s">
-        <v>177</v>
-      </c>
-      <c r="E14" t="s">
-        <v>179</v>
-      </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -4451,48 +4452,48 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" t="s">
         <v>183</v>
       </c>
-      <c r="D15" t="s">
-        <v>187</v>
-      </c>
       <c r="E15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s">
         <v>181</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" t="s">
         <v>185</v>
       </c>
-      <c r="C16" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" t="s">
-        <v>188</v>
-      </c>
-      <c r="E16" t="s">
-        <v>189</v>
-      </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -4532,33 +4533,33 @@
         <v>59</v>
       </c>
       <c r="I1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -4566,25 +4567,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
         <v>66</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>67</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4592,25 +4593,25 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
         <v>68</v>
       </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
       <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" t="s">
         <v>85</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>86</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -4618,25 +4619,25 @@
     </row>
     <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
         <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -4644,25 +4645,25 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
         <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>79</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -4684,246 +4685,246 @@
         <v>57</v>
       </c>
       <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>90</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>91</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>92</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>93</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" t="s">
         <v>94</v>
       </c>
-      <c r="K1" t="s">
-        <v>102</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>95</v>
-      </c>
-      <c r="M1" t="s">
-        <v>96</v>
       </c>
       <c r="N1" t="s">
         <v>59</v>
       </c>
       <c r="O1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" t="s">
         <v>97</v>
       </c>
-      <c r="B2" t="s">
-        <v>99</v>
-      </c>
       <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>103</v>
+      </c>
+      <c r="L2" t="s">
         <v>98</v>
       </c>
-      <c r="D2">
-        <v>100000</v>
-      </c>
-      <c r="E2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2">
-        <v>30000</v>
-      </c>
-      <c r="K2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L2" t="s">
-        <v>100</v>
-      </c>
       <c r="M2">
-        <v>70000</v>
+        <v>70</v>
       </c>
       <c r="N2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D3">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G3">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="N3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D4">
-        <v>200000</v>
+        <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G4">
-        <v>200000</v>
+        <v>200</v>
       </c>
       <c r="N4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D5">
-        <v>50000</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F5" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G5">
-        <v>50000</v>
+        <v>50</v>
       </c>
       <c r="N5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D6">
-        <v>30000</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G6">
-        <v>30000</v>
+        <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D7">
-        <v>15000</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G7">
-        <v>15000</v>
+        <v>15</v>
       </c>
       <c r="N7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D8">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G8">
-        <v>5100</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="I8" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45BF3AD-8CF6-4683-A04E-C55BC4C841FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0590183A-23F4-4AE8-9159-EC6758B62DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="222">
   <si>
     <t>answer_value</t>
   </si>
@@ -2722,6 +2722,264 @@
   </si>
   <si>
     <t>手許資金3,000,000円で、株式会社東京商事を設立した。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発送費</t>
+    <rPh sb="0" eb="3">
+      <t>ハッソウヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>商品を販売した際に生じた</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF767676"/>
+        <rFont val="ＭＳ 明朝"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>送料</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前払金</t>
+    <rPh sb="0" eb="3">
+      <t>マエバライキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品の引渡しを受ける前に支払った代金</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒキワタ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ダイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前受金</t>
+    <rPh sb="0" eb="3">
+      <t>マエウケキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品を引き渡す前に受け取った代金</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ダイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受取商品券</t>
+    <rPh sb="2" eb="5">
+      <t>ショウヒンケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>百貨店などが発行する商品券を所持している場合に使用する勘定科目</t>
+    <rPh sb="0" eb="3">
+      <t>ヒャッカテン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハッコウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ショウヒンケン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品100を仕入れ、代金は掛けとした。なお、運送会社に送料10を現金で支払った。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ダイキン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>ウンソウガイシャ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ソウリョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金、仕入、買掛金、繰越商品</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>カイカケキン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>クリコシショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕入という費用の発生と買掛金という負債の増加、現金という資産の減少です。</t>
+    <rPh sb="0" eb="2">
+      <t>シイレ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カイカケキン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>フサイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>得意先に商品を引き渡す前に現金50を受け取った。</t>
+    <rPh sb="0" eb="3">
+      <t>トクイサキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金、前払金、前受金、仕入</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>マエバライキン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>マエウケキン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金という資産の増加と前受金という負債の増加です。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>マエウケキン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>フサイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ゾウカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2729,7 +2987,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2805,6 +3063,14 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF767676"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3666,16 +3932,72 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C28" s="10"/>
+      <c r="A28" s="1">
+        <v>5</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C29" s="10"/>
+      <c r="A29" s="1">
+        <v>1</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C30" s="10"/>
+      <c r="A30" s="1">
+        <v>2</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C31" s="10"/>
+      <c r="A31" s="1">
+        <v>1</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="10"/>
@@ -4677,7 +4999,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C41FE44F-CD0E-49E1-9F40-FF2D55A2ECFA}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -4927,6 +5249,67 @@
         <v>199</v>
       </c>
     </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9">
+        <v>110</v>
+      </c>
+      <c r="E9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="N9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0590183A-23F4-4AE8-9159-EC6758B62DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DD2B5E-8816-45CF-8AE4-9780E52BDE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="分類問題" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="232">
   <si>
     <t>answer_value</t>
   </si>
@@ -1207,16 +1207,6 @@
       <t>ウリアゲ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>紙幣や硬貨</t>
-    <rPh sb="0" eb="2">
-      <t>シヘイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>備品</t>
@@ -2979,6 +2969,118 @@
     </rPh>
     <rPh sb="20" eb="22">
       <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他人振出小切手、送金小切手、為替証書</t>
+    <rPh sb="0" eb="2">
+      <t>タニン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フリダシ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>コギッテ</t>
+    </rPh>
+    <rPh sb="8" eb="13">
+      <t>ソウキンコギッテ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カワセ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ショウショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>当座預金</t>
+    <rPh sb="0" eb="4">
+      <t>トウザヨキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手形や小切手などの支払いに備えて預け入れておく無利息の預金　</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受取手形</t>
+    <rPh sb="0" eb="2">
+      <t>ウケトリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品販売時に顧客から手形を受け取った際に用いる勘定科目</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ハンバイジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テガタ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支払手形</t>
+    <rPh sb="0" eb="2">
+      <t>シハライ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕入先との通常の営業取引に基づいて生じた手形債務</t>
+  </si>
+  <si>
+    <t>電子記録債権</t>
+    <rPh sb="0" eb="4">
+      <t>デンシキロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電子記録債務</t>
+    <rPh sb="0" eb="4">
+      <t>デンシキロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紙の手形や売掛金に代わる、電子データを活用した新しい金銭債権</t>
+    <rPh sb="7" eb="8">
+      <t>カネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紙の手形や買掛金に代わる、電子データを活用した新しい金銭債務</t>
+    <rPh sb="5" eb="8">
+      <t>カイカケキン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サイム</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3490,7 +3592,7 @@
         <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -3501,7 +3603,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -3603,7 +3705,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>32</v>
@@ -3753,7 +3855,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="1" t="s">
@@ -3768,7 +3870,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="1" t="s">
@@ -3783,10 +3885,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>36</v>
@@ -3800,10 +3902,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>35</v>
@@ -3820,7 +3922,7 @@
         <v>96</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>36</v>
@@ -3834,10 +3936,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>36</v>
@@ -3851,10 +3953,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>36</v>
@@ -3868,10 +3970,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>128</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>36</v>
@@ -3885,10 +3987,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>32</v>
@@ -3905,7 +4007,7 @@
         <v>98</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>33</v>
@@ -3919,10 +4021,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -3936,10 +4038,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>36</v>
@@ -3953,10 +4055,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>32</v>
@@ -3970,10 +4072,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>33</v>
@@ -3987,10 +4089,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>32</v>
@@ -4000,54 +4102,124 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C32" s="10"/>
-    </row>
-    <row r="33" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C33" s="10"/>
-    </row>
-    <row r="34" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C34" s="10"/>
-    </row>
-    <row r="35" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C35" s="10"/>
-    </row>
-    <row r="36" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C36" s="10"/>
-    </row>
-    <row r="37" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="1">
+        <v>1</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="1">
+        <v>1</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="1">
+        <v>2</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="1">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="1">
+        <v>2</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="10"/>
     </row>
-    <row r="38" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="10"/>
     </row>
-    <row r="39" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="10"/>
     </row>
-    <row r="40" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="10"/>
     </row>
-    <row r="41" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="10"/>
     </row>
-    <row r="42" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="10"/>
     </row>
-    <row r="43" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="10"/>
     </row>
-    <row r="44" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="10"/>
     </row>
-    <row r="45" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="10"/>
     </row>
-    <row r="46" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="10"/>
     </row>
-    <row r="47" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="10"/>
     </row>
-    <row r="48" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="10"/>
     </row>
     <row r="49" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -4431,7 +4603,7 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -4494,7 +4666,7 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
         <v>55</v>
@@ -4514,7 +4686,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -4523,16 +4695,16 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" t="s">
         <v>108</v>
-      </c>
-      <c r="E5" t="s">
-        <v>109</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -4540,25 +4712,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" t="s">
         <v>108</v>
-      </c>
-      <c r="E6" t="s">
-        <v>109</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -4566,7 +4738,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
@@ -4575,16 +4747,16 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
         <v>135</v>
-      </c>
-      <c r="E7" t="s">
-        <v>136</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -4592,25 +4764,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" t="s">
         <v>137</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>145</v>
       </c>
-      <c r="C8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>146</v>
       </c>
-      <c r="E8" t="s">
-        <v>147</v>
-      </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -4618,25 +4790,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" t="s">
         <v>139</v>
       </c>
-      <c r="C9" t="s">
-        <v>140</v>
-      </c>
       <c r="D9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" t="s">
         <v>142</v>
-      </c>
-      <c r="E9" t="s">
-        <v>143</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -4644,25 +4816,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" t="s">
         <v>148</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>149</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>150</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>151</v>
-      </c>
-      <c r="E10" t="s">
-        <v>152</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -4670,25 +4842,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
         <v>154</v>
       </c>
-      <c r="B11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>155</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>156</v>
-      </c>
-      <c r="E11" t="s">
-        <v>157</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -4696,25 +4868,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" t="s">
         <v>161</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>162</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>163</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>164</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>165</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -4722,25 +4894,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" t="s">
         <v>166</v>
-      </c>
-      <c r="B13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" t="s">
-        <v>167</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -4748,25 +4920,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" t="s">
         <v>171</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" t="s">
         <v>174</v>
       </c>
-      <c r="C14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" t="s">
-        <v>175</v>
-      </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -4774,48 +4946,48 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s">
         <v>177</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>178</v>
       </c>
-      <c r="C15" t="s">
-        <v>179</v>
-      </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" t="s">
         <v>181</v>
       </c>
-      <c r="C16" t="s">
-        <v>182</v>
-      </c>
       <c r="D16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" t="s">
         <v>184</v>
       </c>
-      <c r="E16" t="s">
-        <v>185</v>
-      </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4858,12 +5030,12 @@
         <v>79</v>
       </c>
       <c r="J1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -5046,12 +5218,12 @@
         <v>59</v>
       </c>
       <c r="O1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
@@ -5081,18 +5253,18 @@
         <v>70</v>
       </c>
       <c r="N2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -5107,12 +5279,12 @@
         <v>100</v>
       </c>
       <c r="N3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
@@ -5127,21 +5299,21 @@
         <v>102</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G4">
         <v>200</v>
       </c>
       <c r="N4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
         <v>101</v>
@@ -5150,33 +5322,33 @@
         <v>50</v>
       </c>
       <c r="E5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" t="s">
         <v>187</v>
-      </c>
-      <c r="F5" t="s">
-        <v>188</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="N5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
         <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>191</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
         <v>101</v>
@@ -5185,15 +5357,15 @@
         <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
         <v>101</v>
@@ -5202,33 +5374,33 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" t="s">
         <v>193</v>
-      </c>
-      <c r="F7" t="s">
-        <v>194</v>
       </c>
       <c r="G7">
         <v>15</v>
       </c>
       <c r="N7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D8">
         <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F8" t="s">
         <v>101</v>
@@ -5237,24 +5409,24 @@
         <v>51</v>
       </c>
       <c r="H8" t="s">
+        <v>196</v>
+      </c>
+      <c r="I8" t="s">
         <v>197</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
         <v>198</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" t="s">
         <v>216</v>
-      </c>
-      <c r="B9" t="s">
-        <v>217</v>
       </c>
       <c r="C9" t="s">
         <v>96</v>
@@ -5263,7 +5435,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F9" t="s">
         <v>98</v>
@@ -5272,7 +5444,7 @@
         <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I9" t="s">
         <v>101</v>
@@ -5281,15 +5453,15 @@
         <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" t="s">
         <v>219</v>
-      </c>
-      <c r="B10" t="s">
-        <v>220</v>
       </c>
       <c r="C10" t="s">
         <v>101</v>
@@ -5298,16 +5470,16 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G10">
         <v>50</v>
       </c>
       <c r="N10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DD2B5E-8816-45CF-8AE4-9780E52BDE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986F1118-F10E-4577-B235-D96C271B2FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="260">
   <si>
     <t>answer_value</t>
   </si>
@@ -3081,6 +3081,344 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>サイム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定資産売却益</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>バイキャクエキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有形固定資産を取得時より高い金額で売却した際に使用する勘定科目</t>
+    <rPh sb="0" eb="6">
+      <t>ユウケイコテイシサン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シュトクジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バイキャク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定資産売却損</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有形固定資産を取得時より低い金額で売却した際に使用する勘定科目</t>
+    <rPh sb="0" eb="6">
+      <t>ユウケイコテイシサン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シュトクジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バイキャク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修繕費</t>
+    <rPh sb="0" eb="3">
+      <t>シュウゼンヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物、備品等の部分的破損を修理し、原状回復させるための支出</t>
+  </si>
+  <si>
+    <t>クレジット売掛金</t>
+    <rPh sb="5" eb="8">
+      <t>ウリカケキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>信販会社に対する将来の入金予定額</t>
+    <rPh sb="0" eb="4">
+      <t>シンパンガイシャ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウキン</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ヨテイガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手形貸付金</t>
+    <rPh sb="0" eb="2">
+      <t>テガタ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カシツケキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>借用証書に代えて手形によって金銭を貸し付けた際に使用する勘定科目</t>
+  </si>
+  <si>
+    <t>手形借入金</t>
+    <rPh sb="0" eb="2">
+      <t>テガタ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カリイレキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>借用証書に代えて手形によって金銭を借り入れた際に使用する勘定科目</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮払金</t>
+    <rPh sb="0" eb="3">
+      <t>カリバライキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一時的に支出した金額で、用途や最終的な勘定科目や金額が未確定のもの</t>
+    <rPh sb="24" eb="26">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮受金</t>
+    <rPh sb="0" eb="3">
+      <t>カリウケキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入金額のうち、入金理由やどの売掛金に対するものかが未確定のもの</t>
+    <rPh sb="0" eb="3">
+      <t>ニュウキンガク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウキン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ウリカケキン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立替金</t>
+    <rPh sb="0" eb="3">
+      <t>タテカエキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一時的に生ずる金銭の立替</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>預り金</t>
+    <rPh sb="0" eb="1">
+      <t>アズカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員の源泉所得税、社会保険料など一時的に預かっている金銭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>法定福利費</t>
+    <rPh sb="0" eb="2">
+      <t>ホウテイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>フクリヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社会保険料の企業負担額、預り金と共に支払う</t>
+    <rPh sb="0" eb="5">
+      <t>シャカイホケンリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>フタンガク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アズカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>差入保証金</t>
+    <rPh sb="0" eb="2">
+      <t>サシイレ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホショウキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>契約や取引において相手方に支払った金額で、通常は契約終了時に返還される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未収入金</t>
+    <rPh sb="0" eb="4">
+      <t>ミシュウニュウキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備品など商品以外の物を売却して、代金は後日受け取る際に使用する勘定科目</t>
+    <rPh sb="4" eb="6">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バイキャク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ダイキン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゴジツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未払金</t>
+    <rPh sb="0" eb="3">
+      <t>ミバライキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>消耗品や備品など商品以外のものを購入して、代金は後日支払う際に使用する勘定科目</t>
+    <rPh sb="0" eb="3">
+      <t>ショウモウヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ビヒン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ショウヒンイガイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ダイキン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゴジツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="35" eb="39">
+      <t>カンジョウカモク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4187,87 +4525,268 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C37" s="10"/>
+      <c r="A37" s="1">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C38" s="10"/>
+      <c r="A38" s="1">
+        <v>5</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C39" s="10"/>
+      <c r="A39" s="1">
+        <v>5</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C40" s="10"/>
+      <c r="A40" s="1">
+        <v>1</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C41" s="10"/>
+      <c r="A41" s="1">
+        <v>1</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C42" s="10"/>
+      <c r="A42" s="1">
+        <v>2</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C43" s="10"/>
+      <c r="A43" s="1">
+        <v>1</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C44" s="10"/>
+      <c r="A44" s="1">
+        <v>2</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C45" s="10"/>
+      <c r="A45" s="1">
+        <v>1</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C46" s="10"/>
+      <c r="A46" s="1">
+        <v>2</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C47" s="10"/>
+      <c r="A47" s="1">
+        <v>5</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C48" s="10"/>
-    </row>
-    <row r="49" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C49" s="10"/>
-    </row>
-    <row r="50" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C50" s="10"/>
-    </row>
-    <row r="51" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="1">
+        <v>1</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="1">
+        <v>1</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="1">
+        <v>2</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="10"/>
     </row>
-    <row r="52" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="10"/>
     </row>
-    <row r="53" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="10"/>
     </row>
-    <row r="54" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="10"/>
     </row>
-    <row r="55" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="10"/>
     </row>
-    <row r="56" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="10"/>
     </row>
-    <row r="57" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="10"/>
     </row>
-    <row r="58" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="10"/>
     </row>
-    <row r="59" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="10"/>
     </row>
-    <row r="60" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="10"/>
     </row>
-    <row r="61" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="10"/>
     </row>
-    <row r="62" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="10"/>
     </row>
-    <row r="63" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="10"/>
     </row>
-    <row r="64" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="10"/>
     </row>
     <row r="65" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986F1118-F10E-4577-B235-D96C271B2FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABFBE2C-416F-48D3-A2ED-F9E0A7322DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="267">
   <si>
     <t>answer_value</t>
   </si>
@@ -3419,6 +3419,145 @@
     </rPh>
     <rPh sb="35" eb="39">
       <t>カンジョウカモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>印紙代、固定資産税、自動車税、不動産取得税、登録免許税等の業務上必要な税金</t>
+    <rPh sb="35" eb="37">
+      <t>ゼイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮払消費税</t>
+    <rPh sb="0" eb="2">
+      <t>カリバラ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ショウヒゼイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品仕入時にかかった消費税を税抜方式で行っている際に使用する勘定科目</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シイレジ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ショウヒゼイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゼイヌ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮受消費税</t>
+    <rPh sb="0" eb="2">
+      <t>カリウケ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゼイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品販売時にお客さんから預かった消費税を一時的に計上するための勘定科目</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンバイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アズ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ショウヒゼイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イチジ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケイジョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未払消費税</t>
+    <rPh sb="0" eb="2">
+      <t>ミバラ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ショウヒゼイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮受消費税から仮払消費税を差引いた残額で、後日納付するもの</t>
+    <rPh sb="0" eb="5">
+      <t>カリウケショウヒゼイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カリバラ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ショウヒゼイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サシヒ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ガク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゴジツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ノウフ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4721,11 +4860,14 @@
       <c r="C48" s="1" t="s">
         <v>255</v>
       </c>
+      <c r="D48" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="E48" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -4735,8 +4877,11 @@
       <c r="C49" s="1" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D49" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>2</v>
       </c>
@@ -4746,47 +4891,94 @@
       <c r="C50" s="1" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C51" s="10"/>
-    </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C53" s="10"/>
-    </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D50" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="1">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="1">
+        <v>1</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="1">
+        <v>2</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="1">
+        <v>2</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="10"/>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="10"/>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="10"/>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="10"/>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="10"/>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="10"/>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="10"/>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="10"/>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="10"/>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="10"/>
     </row>
     <row r="65" spans="3:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABFBE2C-416F-48D3-A2ED-F9E0A7322DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7A26D2-8D40-4C29-82CC-70997BEECB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="分類問題" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="269">
   <si>
     <t>answer_value</t>
   </si>
@@ -2832,34 +2832,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>商品100を仕入れ、代金は掛けとした。なお、運送会社に送料10を現金で支払った。</t>
-    <rPh sb="0" eb="2">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ダイキン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="22" eb="26">
-      <t>ウンソウガイシャ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ソウリョウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>シハラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現金、仕入、買掛金、繰越商品</t>
     <rPh sb="0" eb="2">
       <t>ゲンキン</t>
@@ -3558,6 +3530,66 @@
     </rPh>
     <rPh sb="23" eb="25">
       <t>ノウフ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品100を仕入れ、代金は掛けとした。なお、運送会社に送料10を現金で支払った。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ダイキン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ウンソウガイシャ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ソウリョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,仕入,買掛金,繰越商品</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>カイカケキン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>クリコシショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,前払金,前受金,仕入</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>マエバライキン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>マエウケキン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4080,7 +4112,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -4583,10 +4615,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>32</v>
@@ -4600,10 +4632,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>32</v>
@@ -4617,10 +4649,10 @@
         <v>2</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>33</v>
@@ -4634,10 +4666,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>32</v>
@@ -4651,10 +4683,10 @@
         <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>33</v>
@@ -4668,10 +4700,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>35</v>
@@ -4685,10 +4717,10 @@
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>36</v>
@@ -4702,10 +4734,10 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>36</v>
@@ -4719,10 +4751,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>32</v>
@@ -4736,10 +4768,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>32</v>
@@ -4753,10 +4785,10 @@
         <v>2</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>33</v>
@@ -4770,10 +4802,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>32</v>
@@ -4787,10 +4819,10 @@
         <v>2</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>33</v>
@@ -4804,10 +4836,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>32</v>
@@ -4821,10 +4853,10 @@
         <v>2</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>33</v>
@@ -4838,10 +4870,10 @@
         <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>36</v>
@@ -4855,10 +4887,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>32</v>
@@ -4872,10 +4904,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>32</v>
@@ -4886,10 +4918,10 @@
         <v>2</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>33</v>
@@ -4903,7 +4935,7 @@
         <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>36</v>
@@ -4914,10 +4946,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>32</v>
@@ -4928,10 +4960,10 @@
         <v>2</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>33</v>
@@ -4942,10 +4974,10 @@
         <v>2</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>33</v>
@@ -6134,10 +6166,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" t="s">
         <v>215</v>
-      </c>
-      <c r="B9" t="s">
-        <v>216</v>
       </c>
       <c r="C9" t="s">
         <v>96</v>
@@ -6146,7 +6178,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="F9" t="s">
         <v>98</v>
@@ -6155,7 +6187,7 @@
         <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="I9" t="s">
         <v>101</v>
@@ -6164,15 +6196,15 @@
         <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" t="s">
         <v>218</v>
-      </c>
-      <c r="B10" t="s">
-        <v>219</v>
       </c>
       <c r="C10" t="s">
         <v>101</v>
@@ -6181,7 +6213,7 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>268</v>
       </c>
       <c r="F10" t="s">
         <v>211</v>
@@ -6190,7 +6222,7 @@
         <v>50</v>
       </c>
       <c r="N10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7A26D2-8D40-4C29-82CC-70997BEECB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548383B9-BADB-476A-8109-1ACC65ED9CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
@@ -6186,13 +6186,13 @@
       <c r="G9">
         <v>100</v>
       </c>
-      <c r="H9" t="s">
+      <c r="K9" t="s">
         <v>267</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
         <v>101</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>10</v>
       </c>
       <c r="N9" t="s">

--- a/material_boki3.xlsx
+++ b/material_boki3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mr_sh\Desktop\bokiapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548383B9-BADB-476A-8109-1ACC65ED9CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DADA21D-BA5F-4B68-A0E0-E1772D2B1B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE4C0FF7-C6FC-428E-A421-B60F5DF5D3D8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="267">
   <si>
     <t>answer_value</t>
   </si>
@@ -2400,22 +2400,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>現金,資本金,給料,雑費）</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>シホンキン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>キュウリョウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ザッピ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>給料</t>
     <rPh sb="0" eb="2">
       <t>キュウリョウ</t>
@@ -2445,28 +2429,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>現金,支払手数料,手数料,受取手数料）</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シハラ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>テスウリョウ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>テスウリョウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ウケトリ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>テスウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>受取手数料</t>
     <rPh sb="0" eb="2">
       <t>ウケトリ</t>
@@ -2526,28 +2488,6 @@
     </rPh>
     <rPh sb="31" eb="33">
       <t>ゾウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現金,借入金,支払利息,受取利息）</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>カリイレキン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シハライ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>リソク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ウケトリ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>リソク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2832,22 +2772,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>現金、仕入、買掛金、繰越商品</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シイ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>カイカケキン</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>クリコシショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>仕入という費用の発生と買掛金という負債の増加、現金という資産の減少です。</t>
     <rPh sb="0" eb="2">
       <t>シイレ</t>
@@ -2907,22 +2831,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>現金、前払金、前受金、仕入</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンキン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>マエバライキン</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>マエウケキン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現金という資産の増加と前受金という負債の増加です。</t>
     <rPh sb="0" eb="2">
       <t>ゲンキン</t>
@@ -3590,6 +3498,66 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>シイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,資本金,給料,雑費</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シホンキン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キュウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ザッピ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,支払手数料,手数料,受取手数料</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>テスウリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>テスウリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ウケトリ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>テスウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現金,借入金,支払利息,受取利息</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンキン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カリイレキン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シハライ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リソク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ウケトリ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>リソク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4112,7 +4080,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -4547,10 +4515,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>36</v>
@@ -4564,10 +4532,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>32</v>
@@ -4581,10 +4549,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>33</v>
@@ -4598,10 +4566,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>32</v>
@@ -4615,10 +4583,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>32</v>
@@ -4632,10 +4600,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>32</v>
@@ -4649,10 +4617,10 @@
         <v>2</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>33</v>
@@ -4666,10 +4634,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>32</v>
@@ -4683,10 +4651,10 @@
         <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>33</v>
@@ -4700,10 +4668,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>35</v>
@@ -4717,10 +4685,10 @@
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>36</v>
@@ -4734,10 +4702,10 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>36</v>
@@ -4751,10 +4719,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>32</v>
@@ -4768,10 +4736,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>32</v>
@@ -4785,10 +4753,10 @@
         <v>2</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>33</v>
@@ -4802,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>32</v>
@@ -4819,10 +4787,10 @@
         <v>2</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>33</v>
@@ -4836,10 +4804,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>32</v>
@@ -4853,10 +4821,10 @@
         <v>2</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>33</v>
@@ -4870,10 +4838,10 @@
         <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>36</v>
@@ -4887,10 +4855,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>32</v>
@@ -4904,10 +4872,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>32</v>
@@ -4918,10 +4886,10 @@
         <v>2</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>33</v>
@@ -4935,7 +4903,7 @@
         <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>36</v>
@@ -4946,10 +4914,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>32</v>
@@ -4960,10 +4928,10 @@
         <v>2</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>33</v>
@@ -4974,10 +4942,10 @@
         <v>2</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>33</v>
@@ -5778,7 +5746,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -5916,6 +5884,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C41FE44F-CD0E-49E1-9F40-FF2D55A2ECFA}">
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="78.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -5966,7 +5949,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
@@ -5996,12 +5979,12 @@
         <v>70</v>
       </c>
       <c r="N2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
@@ -6027,7 +6010,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
@@ -6053,7 +6036,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B5" t="s">
         <v>186</v>
@@ -6079,19 +6062,19 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" t="s">
         <v>189</v>
-      </c>
-      <c r="C6" t="s">
-        <v>190</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>189</v>
+        <v>264</v>
       </c>
       <c r="F6" t="s">
         <v>101</v>
@@ -6100,15 +6083,15 @@
         <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="C7" t="s">
         <v>101</v>
@@ -6117,24 +6100,24 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G7">
         <v>15</v>
       </c>
       <c r="N7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="C8" t="s">
         <v>187</v>
@@ -6143,7 +6126,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="F8" t="s">
         <v>101</v>
@@ -6152,24 +6135,24 @@
         <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="I8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="C9" t="s">
         <v>96</v>
@@ -6178,7 +6161,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F9" t="s">
         <v>98</v>
@@ -6187,7 +6170,7 @@
         <v>100</v>
       </c>
       <c r="K9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="L9" t="s">
         <v>101</v>
@@ -6196,15 +6179,15 @@
         <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="C10" t="s">
         <v>101</v>
@@ -6213,16 +6196,16 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G10">
         <v>50</v>
       </c>
       <c r="N10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
